--- a/filer/26121264_dcrown.xlsx
+++ b/filer/26121264_dcrown.xlsx
@@ -7309,7 +7309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7445,24 +7445,24 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
+          <t>fsa:LongtermParticipatingInterests</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
+          <t>fsa:LongtermParticipatingInterests</t>
         </is>
       </c>
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
       <c r="F5" s="35" t="n">
-        <v>16000</v>
+        <v>187000</v>
       </c>
       <c r="G5" s="35" t="n">
-        <v>-209000</v>
+        <v>141000</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>104000</v>
+        <v>146000</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7478,24 +7478,28 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermParticipatingInterests</t>
+          <t>fsa:OtherLongtermDebtRaisedByIssuanceOfBonds</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="38" t="n"/>
+          <t>fsa:OtherLongtermDebtRaisedByIssuanceOfBonds</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n">
+        <v>3492000</v>
+      </c>
+      <c r="E6" s="38" t="n">
+        <v>2158000</v>
+      </c>
       <c r="F6" s="38" t="n">
-        <v>187000</v>
+        <v>4875000</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>141000</v>
+        <v>4655000</v>
       </c>
       <c r="H6" s="38" t="n">
-        <v>146000</v>
+        <v>2539000</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
@@ -7511,21 +7515,27 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>fsa:OtherInvestmentAssets</t>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>fsa:OtherInvestmentAssets</t>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
       <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
+      <c r="E7" s="35" t="n">
+        <v>58000</v>
+      </c>
       <c r="F7" s="35" t="n">
-        <v>67000</v>
-      </c>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
+        <v>16000</v>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>68000</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>17000</v>
+      </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7540,29 +7550,21 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>fsa:OtherLongtermDebtRaisedByIssuanceOfBonds</t>
+          <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>fsa:OtherLongtermDebtRaisedByIssuanceOfBonds</t>
+          <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>3492000</v>
-      </c>
-      <c r="E8" s="38" t="n">
-        <v>2158000</v>
-      </c>
-      <c r="F8" s="38" t="n">
-        <v>4875000</v>
-      </c>
-      <c r="G8" s="38" t="n">
-        <v>4655000</v>
-      </c>
-      <c r="H8" s="38" t="n">
-        <v>2539000</v>
-      </c>
+        <v>29000</v>
+      </c>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="38" t="n"/>
+      <c r="H8" s="38" t="n"/>
       <c r="I8" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7577,27 +7579,25 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
       <c r="D9" s="35" t="n"/>
       <c r="E9" s="35" t="n">
-        <v>58000</v>
+        <v>72000</v>
       </c>
       <c r="F9" s="35" t="n">
-        <v>16000</v>
+        <v>27000</v>
       </c>
       <c r="G9" s="35" t="n">
-        <v>68000</v>
-      </c>
-      <c r="H9" s="35" t="n">
-        <v>17000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H9" s="35" t="n"/>
       <c r="I9" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7612,90 +7612,28 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToAssociates</t>
+          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>fsa:ShorttermPayablesToAssociates</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="n">
-        <v>29000</v>
-      </c>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
+          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="38" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F10" s="38" t="n">
+        <v>41000</v>
+      </c>
+      <c r="G10" s="38" t="n">
+        <v>42000</v>
+      </c>
+      <c r="H10" s="38" t="n">
+        <v>19000</v>
+      </c>
       <c r="I10" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
-        </is>
-      </c>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F11" s="35" t="n">
-        <v>27000</v>
-      </c>
-      <c r="G11" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="38" t="n">
-        <v>21000</v>
-      </c>
-      <c r="F12" s="38" t="n">
-        <v>41000</v>
-      </c>
-      <c r="G12" s="38" t="n">
-        <v>42000</v>
-      </c>
-      <c r="H12" s="38" t="n">
-        <v>19000</v>
-      </c>
-      <c r="I12" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/26121264_dcrown.xlsx
+++ b/filer/26121264_dcrown.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision · Regnskabsår 1/10–30/9 (forskudt)</t>
         </is>
       </c>
     </row>

--- a/filer/26121264_dcrown.xlsx
+++ b/filer/26121264_dcrown.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4579,6 +4579,13 @@
       <c r="F94" s="13">
         <f>IFERROR($F$34/($F$56+$F$63)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
